--- a/Output/Empty Location/Empty Location.xlsx
+++ b/Output/Empty Location/Empty Location.xlsx
@@ -400,7 +400,7 @@
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
   <dimension ref="A1:A193"/>
   <cols>
-    <col min="1" max="1" width="20.83203125" customWidth="1"/>
+    <col min="1" max="1" width="20.5" customWidth="1"/>
   </cols>
   <sheetData>
     <row r="1">
